--- a/files/temp_files/statement_2026_03.xlsx
+++ b/files/temp_files/statement_2026_03.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>286.12</v>
+        <v>-286.12</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>42.94</v>
+        <v>-42.94</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>104.33</v>
+        <v>-104.33</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>40.35</v>
+        <v>-40.35</v>
       </c>
       <c r="D5" t="s">
         <v>62</v>
@@ -653,7 +653,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>359.25</v>
+        <v>-359.25</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -681,7 +681,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>140.38</v>
+        <v>-140.38</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
@@ -695,7 +695,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>468.3</v>
+        <v>-468.3</v>
       </c>
       <c r="D9" t="s">
         <v>59</v>
@@ -709,7 +709,7 @@
         <v>41</v>
       </c>
       <c r="C10">
-        <v>448.78</v>
+        <v>-448.78</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -723,7 +723,7 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>94.61</v>
+        <v>-94.61</v>
       </c>
       <c r="D11" t="s">
         <v>64</v>
@@ -737,7 +737,7 @@
         <v>42</v>
       </c>
       <c r="C12">
-        <v>144.88</v>
+        <v>-144.88</v>
       </c>
       <c r="D12" t="s">
         <v>65</v>
@@ -765,7 +765,7 @@
         <v>40</v>
       </c>
       <c r="C14">
-        <v>67.88</v>
+        <v>-67.88</v>
       </c>
       <c r="D14" t="s">
         <v>61</v>
@@ -779,7 +779,7 @@
         <v>35</v>
       </c>
       <c r="C15">
-        <v>380.34</v>
+        <v>-380.34</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -807,7 +807,7 @@
         <v>38</v>
       </c>
       <c r="C17">
-        <v>157.39</v>
+        <v>-157.39</v>
       </c>
       <c r="D17" t="s">
         <v>62</v>
@@ -821,7 +821,7 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>16.28</v>
+        <v>-16.28</v>
       </c>
       <c r="D18" t="s">
         <v>60</v>
@@ -835,7 +835,7 @@
         <v>35</v>
       </c>
       <c r="C19">
-        <v>85.26000000000001</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
@@ -849,7 +849,7 @@
         <v>42</v>
       </c>
       <c r="C20">
-        <v>125.5</v>
+        <v>-125.5</v>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -863,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="C21">
-        <v>421.36</v>
+        <v>-421.36</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -891,7 +891,7 @@
         <v>40</v>
       </c>
       <c r="C23">
-        <v>155.66</v>
+        <v>-155.66</v>
       </c>
       <c r="D23" t="s">
         <v>61</v>
@@ -905,7 +905,7 @@
         <v>46</v>
       </c>
       <c r="C24">
-        <v>282.73</v>
+        <v>-282.73</v>
       </c>
       <c r="D24" t="s">
         <v>61</v>
@@ -933,7 +933,7 @@
         <v>41</v>
       </c>
       <c r="C26">
-        <v>277.87</v>
+        <v>-277.87</v>
       </c>
       <c r="D26" t="s">
         <v>64</v>
@@ -947,7 +947,7 @@
         <v>42</v>
       </c>
       <c r="C27">
-        <v>42.71</v>
+        <v>-42.71</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -961,7 +961,7 @@
         <v>47</v>
       </c>
       <c r="C28">
-        <v>135.38</v>
+        <v>-135.38</v>
       </c>
       <c r="D28" t="s">
         <v>64</v>
@@ -989,7 +989,7 @@
         <v>46</v>
       </c>
       <c r="C30">
-        <v>286.23</v>
+        <v>-286.23</v>
       </c>
       <c r="D30" t="s">
         <v>61</v>
@@ -1003,7 +1003,7 @@
         <v>48</v>
       </c>
       <c r="C31">
-        <v>47.19</v>
+        <v>-47.19</v>
       </c>
       <c r="D31" t="s">
         <v>66</v>
@@ -1017,7 +1017,7 @@
         <v>44</v>
       </c>
       <c r="C32">
-        <v>39.58</v>
+        <v>-39.58</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1031,7 +1031,7 @@
         <v>49</v>
       </c>
       <c r="C33">
-        <v>66.14</v>
+        <v>-66.14</v>
       </c>
       <c r="D33" t="s">
         <v>66</v>
@@ -1059,7 +1059,7 @@
         <v>47</v>
       </c>
       <c r="C35">
-        <v>671.6799999999999</v>
+        <v>-671.6799999999999</v>
       </c>
       <c r="D35" t="s">
         <v>64</v>
@@ -1073,7 +1073,7 @@
         <v>40</v>
       </c>
       <c r="C36">
-        <v>179.56</v>
+        <v>-179.56</v>
       </c>
       <c r="D36" t="s">
         <v>61</v>
@@ -1087,7 +1087,7 @@
         <v>50</v>
       </c>
       <c r="C37">
-        <v>50.31</v>
+        <v>-50.31</v>
       </c>
       <c r="D37" t="s">
         <v>65</v>
@@ -1101,7 +1101,7 @@
         <v>47</v>
       </c>
       <c r="C38">
-        <v>633.34</v>
+        <v>-633.34</v>
       </c>
       <c r="D38" t="s">
         <v>64</v>
@@ -1115,7 +1115,7 @@
         <v>51</v>
       </c>
       <c r="C39">
-        <v>42.83</v>
+        <v>-42.83</v>
       </c>
       <c r="D39" t="s">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         <v>52</v>
       </c>
       <c r="C40">
-        <v>46.81</v>
+        <v>-46.81</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -1143,7 +1143,7 @@
         <v>36</v>
       </c>
       <c r="C41">
-        <v>49.46</v>
+        <v>-49.46</v>
       </c>
       <c r="D41" t="s">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         <v>38</v>
       </c>
       <c r="C42">
-        <v>99.61</v>
+        <v>-99.61</v>
       </c>
       <c r="D42" t="s">
         <v>62</v>
@@ -1171,7 +1171,7 @@
         <v>36</v>
       </c>
       <c r="C43">
-        <v>32.45</v>
+        <v>-32.45</v>
       </c>
       <c r="D43" t="s">
         <v>60</v>
@@ -1185,7 +1185,7 @@
         <v>44</v>
       </c>
       <c r="C44">
-        <v>36.03</v>
+        <v>-36.03</v>
       </c>
       <c r="D44" t="s">
         <v>60</v>
@@ -1213,7 +1213,7 @@
         <v>37</v>
       </c>
       <c r="C46">
-        <v>269.47</v>
+        <v>-269.47</v>
       </c>
       <c r="D46" t="s">
         <v>61</v>
@@ -1227,7 +1227,7 @@
         <v>49</v>
       </c>
       <c r="C47">
-        <v>96.73</v>
+        <v>-96.73</v>
       </c>
       <c r="D47" t="s">
         <v>66</v>
@@ -1241,7 +1241,7 @@
         <v>52</v>
       </c>
       <c r="C48">
-        <v>114.01</v>
+        <v>-114.01</v>
       </c>
       <c r="D48" t="s">
         <v>65</v>
@@ -1255,7 +1255,7 @@
         <v>46</v>
       </c>
       <c r="C49">
-        <v>103.98</v>
+        <v>-103.98</v>
       </c>
       <c r="D49" t="s">
         <v>61</v>
@@ -1269,7 +1269,7 @@
         <v>45</v>
       </c>
       <c r="C50">
-        <v>10.37</v>
+        <v>-10.37</v>
       </c>
       <c r="D50" t="s">
         <v>59</v>
@@ -1283,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="C51">
-        <v>67.66</v>
+        <v>-67.66</v>
       </c>
       <c r="D51" t="s">
         <v>66</v>
@@ -1297,7 +1297,7 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>18.75</v>
+        <v>-18.75</v>
       </c>
       <c r="D52" t="s">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="C54">
-        <v>123.02</v>
+        <v>-123.02</v>
       </c>
       <c r="D54" t="s">
         <v>62</v>
@@ -1339,7 +1339,7 @@
         <v>51</v>
       </c>
       <c r="C55">
-        <v>41.07</v>
+        <v>-41.07</v>
       </c>
       <c r="D55" t="s">
         <v>60</v>
@@ -1353,7 +1353,7 @@
         <v>51</v>
       </c>
       <c r="C56">
-        <v>5.31</v>
+        <v>-5.31</v>
       </c>
       <c r="D56" t="s">
         <v>60</v>
@@ -1367,7 +1367,7 @@
         <v>47</v>
       </c>
       <c r="C57">
-        <v>733.23</v>
+        <v>-733.23</v>
       </c>
       <c r="D57" t="s">
         <v>64</v>
@@ -1381,7 +1381,7 @@
         <v>37</v>
       </c>
       <c r="C58">
-        <v>171.31</v>
+        <v>-171.31</v>
       </c>
       <c r="D58" t="s">
         <v>61</v>
@@ -1395,7 +1395,7 @@
         <v>52</v>
       </c>
       <c r="C59">
-        <v>80.45999999999999</v>
+        <v>-80.45999999999999</v>
       </c>
       <c r="D59" t="s">
         <v>65</v>
@@ -1409,7 +1409,7 @@
         <v>37</v>
       </c>
       <c r="C60">
-        <v>97.68000000000001</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="D60" t="s">
         <v>61</v>
@@ -1423,7 +1423,7 @@
         <v>51</v>
       </c>
       <c r="C61">
-        <v>27.19</v>
+        <v>-27.19</v>
       </c>
       <c r="D61" t="s">
         <v>60</v>
@@ -1451,7 +1451,7 @@
         <v>55</v>
       </c>
       <c r="C63">
-        <v>121.51</v>
+        <v>-121.51</v>
       </c>
       <c r="D63" t="s">
         <v>64</v>
@@ -1465,7 +1465,7 @@
         <v>37</v>
       </c>
       <c r="C64">
-        <v>180.23</v>
+        <v>-180.23</v>
       </c>
       <c r="D64" t="s">
         <v>61</v>
@@ -1507,7 +1507,7 @@
         <v>35</v>
       </c>
       <c r="C67">
-        <v>132.71</v>
+        <v>-132.71</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="C68">
-        <v>43.07</v>
+        <v>-43.07</v>
       </c>
       <c r="D68" t="s">
         <v>61</v>
@@ -1535,7 +1535,7 @@
         <v>40</v>
       </c>
       <c r="C69">
-        <v>229.39</v>
+        <v>-229.39</v>
       </c>
       <c r="D69" t="s">
         <v>61</v>
@@ -1549,7 +1549,7 @@
         <v>36</v>
       </c>
       <c r="C70">
-        <v>14.45</v>
+        <v>-14.45</v>
       </c>
       <c r="D70" t="s">
         <v>60</v>
@@ -1563,7 +1563,7 @@
         <v>51</v>
       </c>
       <c r="C71">
-        <v>39.08</v>
+        <v>-39.08</v>
       </c>
       <c r="D71" t="s">
         <v>60</v>
@@ -1577,7 +1577,7 @@
         <v>46</v>
       </c>
       <c r="C72">
-        <v>135.94</v>
+        <v>-135.94</v>
       </c>
       <c r="D72" t="s">
         <v>61</v>
@@ -1591,7 +1591,7 @@
         <v>41</v>
       </c>
       <c r="C73">
-        <v>293.53</v>
+        <v>-293.53</v>
       </c>
       <c r="D73" t="s">
         <v>64</v>
@@ -1619,7 +1619,7 @@
         <v>37</v>
       </c>
       <c r="C75">
-        <v>182.55</v>
+        <v>-182.55</v>
       </c>
       <c r="D75" t="s">
         <v>61</v>
@@ -1647,7 +1647,7 @@
         <v>51</v>
       </c>
       <c r="C77">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="D77" t="s">
         <v>60</v>
@@ -1661,7 +1661,7 @@
         <v>40</v>
       </c>
       <c r="C78">
-        <v>39.09</v>
+        <v>-39.09</v>
       </c>
       <c r="D78" t="s">
         <v>61</v>
@@ -1675,7 +1675,7 @@
         <v>48</v>
       </c>
       <c r="C79">
-        <v>42.24</v>
+        <v>-42.24</v>
       </c>
       <c r="D79" t="s">
         <v>66</v>
@@ -1689,7 +1689,7 @@
         <v>52</v>
       </c>
       <c r="C80">
-        <v>79.56</v>
+        <v>-79.56</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -1703,7 +1703,7 @@
         <v>52</v>
       </c>
       <c r="C81">
-        <v>31.61</v>
+        <v>-31.61</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -1731,7 +1731,7 @@
         <v>48</v>
       </c>
       <c r="C83">
-        <v>30.18</v>
+        <v>-30.18</v>
       </c>
       <c r="D83" t="s">
         <v>66</v>
@@ -1745,7 +1745,7 @@
         <v>40</v>
       </c>
       <c r="C84">
-        <v>242.24</v>
+        <v>-242.24</v>
       </c>
       <c r="D84" t="s">
         <v>61</v>
@@ -1773,7 +1773,7 @@
         <v>36</v>
       </c>
       <c r="C86">
-        <v>47.81</v>
+        <v>-47.81</v>
       </c>
       <c r="D86" t="s">
         <v>60</v>
@@ -1787,7 +1787,7 @@
         <v>41</v>
       </c>
       <c r="C87">
-        <v>107.05</v>
+        <v>-107.05</v>
       </c>
       <c r="D87" t="s">
         <v>64</v>
@@ -1815,7 +1815,7 @@
         <v>54</v>
       </c>
       <c r="C89">
-        <v>81.45999999999999</v>
+        <v>-81.45999999999999</v>
       </c>
       <c r="D89" t="s">
         <v>62</v>
@@ -1829,7 +1829,7 @@
         <v>56</v>
       </c>
       <c r="C90">
-        <v>113.15</v>
+        <v>-113.15</v>
       </c>
       <c r="D90" t="s">
         <v>62</v>
@@ -1843,7 +1843,7 @@
         <v>49</v>
       </c>
       <c r="C91">
-        <v>69.86</v>
+        <v>-69.86</v>
       </c>
       <c r="D91" t="s">
         <v>66</v>
@@ -1871,7 +1871,7 @@
         <v>52</v>
       </c>
       <c r="C93">
-        <v>130.4</v>
+        <v>-130.4</v>
       </c>
       <c r="D93" t="s">
         <v>65</v>
@@ -1885,7 +1885,7 @@
         <v>40</v>
       </c>
       <c r="C94">
-        <v>133.6</v>
+        <v>-133.6</v>
       </c>
       <c r="D94" t="s">
         <v>61</v>
@@ -1899,7 +1899,7 @@
         <v>42</v>
       </c>
       <c r="C95">
-        <v>89.31</v>
+        <v>-89.31</v>
       </c>
       <c r="D95" t="s">
         <v>65</v>
@@ -1913,7 +1913,7 @@
         <v>51</v>
       </c>
       <c r="C96">
-        <v>18.83</v>
+        <v>-18.83</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1927,7 +1927,7 @@
         <v>51</v>
       </c>
       <c r="C97">
-        <v>35.1</v>
+        <v>-35.1</v>
       </c>
       <c r="D97" t="s">
         <v>60</v>
@@ -1941,7 +1941,7 @@
         <v>52</v>
       </c>
       <c r="C98">
-        <v>56.87</v>
+        <v>-56.87</v>
       </c>
       <c r="D98" t="s">
         <v>65</v>
@@ -1955,7 +1955,7 @@
         <v>52</v>
       </c>
       <c r="C99">
-        <v>134.07</v>
+        <v>-134.07</v>
       </c>
       <c r="D99" t="s">
         <v>65</v>
@@ -1969,7 +1969,7 @@
         <v>46</v>
       </c>
       <c r="C100">
-        <v>171.92</v>
+        <v>-171.92</v>
       </c>
       <c r="D100" t="s">
         <v>61</v>
@@ -1983,7 +1983,7 @@
         <v>35</v>
       </c>
       <c r="C101">
-        <v>110.9</v>
+        <v>-110.9</v>
       </c>
       <c r="D101" t="s">
         <v>59</v>
@@ -1997,7 +1997,7 @@
         <v>54</v>
       </c>
       <c r="C102">
-        <v>94.3</v>
+        <v>-94.3</v>
       </c>
       <c r="D102" t="s">
         <v>62</v>
@@ -2011,7 +2011,7 @@
         <v>42</v>
       </c>
       <c r="C103">
-        <v>144.31</v>
+        <v>-144.31</v>
       </c>
       <c r="D103" t="s">
         <v>65</v>
@@ -2039,7 +2039,7 @@
         <v>57</v>
       </c>
       <c r="C105">
-        <v>34.45</v>
+        <v>-34.45</v>
       </c>
       <c r="D105" t="s">
         <v>66</v>
@@ -2053,7 +2053,7 @@
         <v>51</v>
       </c>
       <c r="C106">
-        <v>49.23</v>
+        <v>-49.23</v>
       </c>
       <c r="D106" t="s">
         <v>60</v>
@@ -2067,7 +2067,7 @@
         <v>35</v>
       </c>
       <c r="C107">
-        <v>255.61</v>
+        <v>-255.61</v>
       </c>
       <c r="D107" t="s">
         <v>59</v>
@@ -2081,7 +2081,7 @@
         <v>48</v>
       </c>
       <c r="C108">
-        <v>64.18000000000001</v>
+        <v>-64.18000000000001</v>
       </c>
       <c r="D108" t="s">
         <v>66</v>
@@ -2095,7 +2095,7 @@
         <v>42</v>
       </c>
       <c r="C109">
-        <v>27.23</v>
+        <v>-27.23</v>
       </c>
       <c r="D109" t="s">
         <v>65</v>
@@ -2109,7 +2109,7 @@
         <v>56</v>
       </c>
       <c r="C110">
-        <v>170.99</v>
+        <v>-170.99</v>
       </c>
       <c r="D110" t="s">
         <v>62</v>
@@ -2123,7 +2123,7 @@
         <v>55</v>
       </c>
       <c r="C111">
-        <v>794.78</v>
+        <v>-794.78</v>
       </c>
       <c r="D111" t="s">
         <v>64</v>
@@ -2137,7 +2137,7 @@
         <v>38</v>
       </c>
       <c r="C112">
-        <v>194.29</v>
+        <v>-194.29</v>
       </c>
       <c r="D112" t="s">
         <v>62</v>
@@ -2151,7 +2151,7 @@
         <v>54</v>
       </c>
       <c r="C113">
-        <v>183.72</v>
+        <v>-183.72</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2179,7 +2179,7 @@
         <v>38</v>
       </c>
       <c r="C115">
-        <v>75.61</v>
+        <v>-75.61</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
@@ -2193,7 +2193,7 @@
         <v>47</v>
       </c>
       <c r="C116">
-        <v>958.47</v>
+        <v>-958.47</v>
       </c>
       <c r="D116" t="s">
         <v>64</v>
@@ -2207,7 +2207,7 @@
         <v>41</v>
       </c>
       <c r="C117">
-        <v>566.53</v>
+        <v>-566.53</v>
       </c>
       <c r="D117" t="s">
         <v>64</v>
@@ -2221,7 +2221,7 @@
         <v>40</v>
       </c>
       <c r="C118">
-        <v>293.65</v>
+        <v>-293.65</v>
       </c>
       <c r="D118" t="s">
         <v>61</v>
@@ -2235,7 +2235,7 @@
         <v>36</v>
       </c>
       <c r="C119">
-        <v>15.23</v>
+        <v>-15.23</v>
       </c>
       <c r="D119" t="s">
         <v>60</v>
@@ -2249,7 +2249,7 @@
         <v>55</v>
       </c>
       <c r="C120">
-        <v>311.31</v>
+        <v>-311.31</v>
       </c>
       <c r="D120" t="s">
         <v>64</v>
@@ -2263,7 +2263,7 @@
         <v>37</v>
       </c>
       <c r="C121">
-        <v>233.34</v>
+        <v>-233.34</v>
       </c>
       <c r="D121" t="s">
         <v>61</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="C122">
-        <v>599.88</v>
+        <v>-599.88</v>
       </c>
       <c r="D122" t="s">
         <v>64</v>
@@ -2291,7 +2291,7 @@
         <v>35</v>
       </c>
       <c r="C123">
-        <v>316.43</v>
+        <v>-316.43</v>
       </c>
       <c r="D123" t="s">
         <v>59</v>
@@ -2319,7 +2319,7 @@
         <v>42</v>
       </c>
       <c r="C125">
-        <v>56.43</v>
+        <v>-56.43</v>
       </c>
       <c r="D125" t="s">
         <v>65</v>
@@ -2347,7 +2347,7 @@
         <v>48</v>
       </c>
       <c r="C127">
-        <v>94.84999999999999</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="D127" t="s">
         <v>66</v>
@@ -2361,7 +2361,7 @@
         <v>35</v>
       </c>
       <c r="C128">
-        <v>485.06</v>
+        <v>-485.06</v>
       </c>
       <c r="D128" t="s">
         <v>59</v>
@@ -2375,7 +2375,7 @@
         <v>40</v>
       </c>
       <c r="C129">
-        <v>238.51</v>
+        <v>-238.51</v>
       </c>
       <c r="D129" t="s">
         <v>61</v>
@@ -2389,7 +2389,7 @@
         <v>58</v>
       </c>
       <c r="C130">
-        <v>54.66</v>
+        <v>-54.66</v>
       </c>
       <c r="D130" t="s">
         <v>59</v>
@@ -2403,7 +2403,7 @@
         <v>47</v>
       </c>
       <c r="C131">
-        <v>209.33</v>
+        <v>-209.33</v>
       </c>
       <c r="D131" t="s">
         <v>64</v>
@@ -2417,7 +2417,7 @@
         <v>55</v>
       </c>
       <c r="C132">
-        <v>231.48</v>
+        <v>-231.48</v>
       </c>
       <c r="D132" t="s">
         <v>64</v>
@@ -2431,7 +2431,7 @@
         <v>42</v>
       </c>
       <c r="C133">
-        <v>33.8</v>
+        <v>-33.8</v>
       </c>
       <c r="D133" t="s">
         <v>65</v>
@@ -2459,7 +2459,7 @@
         <v>46</v>
       </c>
       <c r="C135">
-        <v>174.46</v>
+        <v>-174.46</v>
       </c>
       <c r="D135" t="s">
         <v>61</v>
@@ -2473,7 +2473,7 @@
         <v>36</v>
       </c>
       <c r="C136">
-        <v>11.59</v>
+        <v>-11.59</v>
       </c>
       <c r="D136" t="s">
         <v>60</v>
@@ -2487,7 +2487,7 @@
         <v>36</v>
       </c>
       <c r="C137">
-        <v>30.95</v>
+        <v>-30.95</v>
       </c>
       <c r="D137" t="s">
         <v>60</v>
@@ -2529,7 +2529,7 @@
         <v>55</v>
       </c>
       <c r="C140">
-        <v>418.87</v>
+        <v>-418.87</v>
       </c>
       <c r="D140" t="s">
         <v>64</v>
@@ -2543,7 +2543,7 @@
         <v>37</v>
       </c>
       <c r="C141">
-        <v>138.97</v>
+        <v>-138.97</v>
       </c>
       <c r="D141" t="s">
         <v>61</v>
@@ -2557,7 +2557,7 @@
         <v>49</v>
       </c>
       <c r="C142">
-        <v>56.88</v>
+        <v>-56.88</v>
       </c>
       <c r="D142" t="s">
         <v>66</v>
@@ -2571,7 +2571,7 @@
         <v>49</v>
       </c>
       <c r="C143">
-        <v>25.26</v>
+        <v>-25.26</v>
       </c>
       <c r="D143" t="s">
         <v>66</v>
@@ -2585,7 +2585,7 @@
         <v>47</v>
       </c>
       <c r="C144">
-        <v>718.4299999999999</v>
+        <v>-718.4299999999999</v>
       </c>
       <c r="D144" t="s">
         <v>64</v>
@@ -2599,7 +2599,7 @@
         <v>57</v>
       </c>
       <c r="C145">
-        <v>13.61</v>
+        <v>-13.61</v>
       </c>
       <c r="D145" t="s">
         <v>66</v>
@@ -2613,7 +2613,7 @@
         <v>52</v>
       </c>
       <c r="C146">
-        <v>127.42</v>
+        <v>-127.42</v>
       </c>
       <c r="D146" t="s">
         <v>65</v>
@@ -2627,7 +2627,7 @@
         <v>40</v>
       </c>
       <c r="C147">
-        <v>269.32</v>
+        <v>-269.32</v>
       </c>
       <c r="D147" t="s">
         <v>61</v>
@@ -2641,7 +2641,7 @@
         <v>55</v>
       </c>
       <c r="C148">
-        <v>296</v>
+        <v>-296</v>
       </c>
       <c r="D148" t="s">
         <v>64</v>
@@ -2655,7 +2655,7 @@
         <v>52</v>
       </c>
       <c r="C149">
-        <v>144.97</v>
+        <v>-144.97</v>
       </c>
       <c r="D149" t="s">
         <v>65</v>
@@ -2669,7 +2669,7 @@
         <v>42</v>
       </c>
       <c r="C150">
-        <v>80.48</v>
+        <v>-80.48</v>
       </c>
       <c r="D150" t="s">
         <v>65</v>
@@ -2683,7 +2683,7 @@
         <v>46</v>
       </c>
       <c r="C151">
-        <v>174.86</v>
+        <v>-174.86</v>
       </c>
       <c r="D151" t="s">
         <v>61</v>
@@ -2697,7 +2697,7 @@
         <v>51</v>
       </c>
       <c r="C152">
-        <v>26.83</v>
+        <v>-26.83</v>
       </c>
       <c r="D152" t="s">
         <v>60</v>
@@ -2711,7 +2711,7 @@
         <v>42</v>
       </c>
       <c r="C153">
-        <v>141.92</v>
+        <v>-141.92</v>
       </c>
       <c r="D153" t="s">
         <v>65</v>
@@ -2725,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="C154">
-        <v>402.35</v>
+        <v>-402.35</v>
       </c>
       <c r="D154" t="s">
         <v>64</v>
@@ -2739,7 +2739,7 @@
         <v>40</v>
       </c>
       <c r="C155">
-        <v>150.13</v>
+        <v>-150.13</v>
       </c>
       <c r="D155" t="s">
         <v>61</v>
@@ -2753,7 +2753,7 @@
         <v>40</v>
       </c>
       <c r="C156">
-        <v>287.13</v>
+        <v>-287.13</v>
       </c>
       <c r="D156" t="s">
         <v>61</v>
@@ -2767,7 +2767,7 @@
         <v>58</v>
       </c>
       <c r="C157">
-        <v>474.53</v>
+        <v>-474.53</v>
       </c>
       <c r="D157" t="s">
         <v>59</v>
@@ -2781,7 +2781,7 @@
         <v>45</v>
       </c>
       <c r="C158">
-        <v>499.47</v>
+        <v>-499.47</v>
       </c>
       <c r="D158" t="s">
         <v>59</v>
@@ -2795,7 +2795,7 @@
         <v>38</v>
       </c>
       <c r="C159">
-        <v>85.16</v>
+        <v>-85.16</v>
       </c>
       <c r="D159" t="s">
         <v>62</v>
@@ -2809,7 +2809,7 @@
         <v>46</v>
       </c>
       <c r="C160">
-        <v>278.5</v>
+        <v>-278.5</v>
       </c>
       <c r="D160" t="s">
         <v>61</v>
@@ -2837,7 +2837,7 @@
         <v>35</v>
       </c>
       <c r="C162">
-        <v>431</v>
+        <v>-431</v>
       </c>
       <c r="D162" t="s">
         <v>59</v>
@@ -2851,7 +2851,7 @@
         <v>41</v>
       </c>
       <c r="C163">
-        <v>154.75</v>
+        <v>-154.75</v>
       </c>
       <c r="D163" t="s">
         <v>64</v>
@@ -2865,7 +2865,7 @@
         <v>35</v>
       </c>
       <c r="C164">
-        <v>169.44</v>
+        <v>-169.44</v>
       </c>
       <c r="D164" t="s">
         <v>59</v>
@@ -2879,7 +2879,7 @@
         <v>35</v>
       </c>
       <c r="C165">
-        <v>72.7</v>
+        <v>-72.7</v>
       </c>
       <c r="D165" t="s">
         <v>59</v>
@@ -2893,7 +2893,7 @@
         <v>42</v>
       </c>
       <c r="C166">
-        <v>137.79</v>
+        <v>-137.79</v>
       </c>
       <c r="D166" t="s">
         <v>65</v>
@@ -2907,7 +2907,7 @@
         <v>42</v>
       </c>
       <c r="C167">
-        <v>56.22</v>
+        <v>-56.22</v>
       </c>
       <c r="D167" t="s">
         <v>65</v>
@@ -2921,7 +2921,7 @@
         <v>54</v>
       </c>
       <c r="C168">
-        <v>183.28</v>
+        <v>-183.28</v>
       </c>
       <c r="D168" t="s">
         <v>62</v>
@@ -2935,7 +2935,7 @@
         <v>46</v>
       </c>
       <c r="C169">
-        <v>240.63</v>
+        <v>-240.63</v>
       </c>
       <c r="D169" t="s">
         <v>61</v>
@@ -2949,7 +2949,7 @@
         <v>49</v>
       </c>
       <c r="C170">
-        <v>10.17</v>
+        <v>-10.17</v>
       </c>
       <c r="D170" t="s">
         <v>66</v>
@@ -2963,7 +2963,7 @@
         <v>57</v>
       </c>
       <c r="C171">
-        <v>78.5</v>
+        <v>-78.5</v>
       </c>
       <c r="D171" t="s">
         <v>66</v>
@@ -2977,7 +2977,7 @@
         <v>56</v>
       </c>
       <c r="C172">
-        <v>123.48</v>
+        <v>-123.48</v>
       </c>
       <c r="D172" t="s">
         <v>62</v>
@@ -2991,7 +2991,7 @@
         <v>48</v>
       </c>
       <c r="C173">
-        <v>89.87</v>
+        <v>-89.87</v>
       </c>
       <c r="D173" t="s">
         <v>66</v>
@@ -3005,7 +3005,7 @@
         <v>38</v>
       </c>
       <c r="C174">
-        <v>134.89</v>
+        <v>-134.89</v>
       </c>
       <c r="D174" t="s">
         <v>62</v>
@@ -3033,7 +3033,7 @@
         <v>54</v>
       </c>
       <c r="C176">
-        <v>131.77</v>
+        <v>-131.77</v>
       </c>
       <c r="D176" t="s">
         <v>62</v>
@@ -3047,7 +3047,7 @@
         <v>41</v>
       </c>
       <c r="C177">
-        <v>513.35</v>
+        <v>-513.35</v>
       </c>
       <c r="D177" t="s">
         <v>64</v>
@@ -3061,7 +3061,7 @@
         <v>55</v>
       </c>
       <c r="C178">
-        <v>505.6</v>
+        <v>-505.6</v>
       </c>
       <c r="D178" t="s">
         <v>64</v>
@@ -3089,7 +3089,7 @@
         <v>47</v>
       </c>
       <c r="C180">
-        <v>623.39</v>
+        <v>-623.39</v>
       </c>
       <c r="D180" t="s">
         <v>64</v>
@@ -3103,7 +3103,7 @@
         <v>57</v>
       </c>
       <c r="C181">
-        <v>35.01</v>
+        <v>-35.01</v>
       </c>
       <c r="D181" t="s">
         <v>66</v>
@@ -3117,7 +3117,7 @@
         <v>41</v>
       </c>
       <c r="C182">
-        <v>819.4</v>
+        <v>-819.4</v>
       </c>
       <c r="D182" t="s">
         <v>64</v>
@@ -3145,7 +3145,7 @@
         <v>55</v>
       </c>
       <c r="C184">
-        <v>637.9</v>
+        <v>-637.9</v>
       </c>
       <c r="D184" t="s">
         <v>64</v>
@@ -3159,7 +3159,7 @@
         <v>35</v>
       </c>
       <c r="C185">
-        <v>235.32</v>
+        <v>-235.32</v>
       </c>
       <c r="D185" t="s">
         <v>59</v>
@@ -3173,7 +3173,7 @@
         <v>49</v>
       </c>
       <c r="C186">
-        <v>13.93</v>
+        <v>-13.93</v>
       </c>
       <c r="D186" t="s">
         <v>66</v>
@@ -3201,7 +3201,7 @@
         <v>57</v>
       </c>
       <c r="C188">
-        <v>94.20999999999999</v>
+        <v>-94.20999999999999</v>
       </c>
       <c r="D188" t="s">
         <v>66</v>
@@ -3215,7 +3215,7 @@
         <v>49</v>
       </c>
       <c r="C189">
-        <v>79.56999999999999</v>
+        <v>-79.56999999999999</v>
       </c>
       <c r="D189" t="s">
         <v>66</v>
@@ -3229,7 +3229,7 @@
         <v>38</v>
       </c>
       <c r="C190">
-        <v>44.09</v>
+        <v>-44.09</v>
       </c>
       <c r="D190" t="s">
         <v>62</v>
@@ -3243,7 +3243,7 @@
         <v>56</v>
       </c>
       <c r="C191">
-        <v>111.78</v>
+        <v>-111.78</v>
       </c>
       <c r="D191" t="s">
         <v>62</v>
@@ -3257,7 +3257,7 @@
         <v>58</v>
       </c>
       <c r="C192">
-        <v>433.95</v>
+        <v>-433.95</v>
       </c>
       <c r="D192" t="s">
         <v>59</v>
@@ -3271,7 +3271,7 @@
         <v>55</v>
       </c>
       <c r="C193">
-        <v>661.74</v>
+        <v>-661.74</v>
       </c>
       <c r="D193" t="s">
         <v>64</v>
@@ -3285,7 +3285,7 @@
         <v>56</v>
       </c>
       <c r="C194">
-        <v>55.51</v>
+        <v>-55.51</v>
       </c>
       <c r="D194" t="s">
         <v>62</v>
@@ -3299,7 +3299,7 @@
         <v>55</v>
       </c>
       <c r="C195">
-        <v>842.9400000000001</v>
+        <v>-842.9400000000001</v>
       </c>
       <c r="D195" t="s">
         <v>64</v>
@@ -3313,7 +3313,7 @@
         <v>57</v>
       </c>
       <c r="C196">
-        <v>79.97</v>
+        <v>-79.97</v>
       </c>
       <c r="D196" t="s">
         <v>66</v>
@@ -3327,7 +3327,7 @@
         <v>44</v>
       </c>
       <c r="C197">
-        <v>8.76</v>
+        <v>-8.76</v>
       </c>
       <c r="D197" t="s">
         <v>60</v>
@@ -3341,7 +3341,7 @@
         <v>44</v>
       </c>
       <c r="C198">
-        <v>23.96</v>
+        <v>-23.96</v>
       </c>
       <c r="D198" t="s">
         <v>60</v>
@@ -3369,7 +3369,7 @@
         <v>57</v>
       </c>
       <c r="C200">
-        <v>58.17</v>
+        <v>-58.17</v>
       </c>
       <c r="D200" t="s">
         <v>66</v>
@@ -3383,7 +3383,7 @@
         <v>37</v>
       </c>
       <c r="C201">
-        <v>144.19</v>
+        <v>-144.19</v>
       </c>
       <c r="D201" t="s">
         <v>61</v>
